--- a/tests/data_golden/formulas.template.xlsx
+++ b/tests/data_golden/formulas.template.xlsx
@@ -19,13 +19,15 @@
     <sheet name="formulas-rc-subtotal" sheetId="10" r:id="rId13"/>
     <sheet name="formulas-cr-subtotal" sheetId="11" r:id="rId14"/>
     <sheet name="formulas-cc-subtotal" sheetId="12" r:id="rId15"/>
+    <sheet name="formulas-r-above" sheetId="13" r:id="rId16"/>
+    <sheet name="formulas-r-below" sheetId="14" r:id="rId17"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="28">
   <si>
     <t>#{r}${rbitems#r.name}</t>
   </si>
@@ -547,6 +549,75 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="3"/>
+    <col customWidth="true" max="4" min="2" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="C2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="str">
+        <f>C2*C3</f>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="3"/>
+    <col customWidth="true" max="4" min="2" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="str">
+        <f>C2+C5</f>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
